--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -434,14 +434,14 @@
     <t>AssociatedEntity.associatedPerson</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
 </t>
   </si>
   <si>
     <t>AssociatedEntity.scopingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
   </si>
 </sst>
@@ -1019,7 +1019,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1322,7 +1322,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1423,7 +1423,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1526,7 +1526,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -2130,7 +2130,7 @@
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="154">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,10 @@
     <t>InfrastructureRoot.typeId</t>
   </si>
   <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
+  </si>
+  <si>
     <t>AssociatedEntity.typeId.nullFlavor</t>
   </si>
   <si>
@@ -391,10 +395,42 @@
     <t>AssociatedEntity.classCode</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDARoleClassAssociative</t>
+    <t>PS / Non PS La valeur doit être issue du JDV_J141_RoleClass_CISIS (1.2.250.1.213.1.1.5.588).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J141-RoleClass-CISIS/FHIR/JDV-J141-RoleClass-CISIS</t>
   </si>
   <si>
     <t>AssociatedEntity.id</t>
+  </si>
+  <si>
+    <t>Identifiant du participant Obligatoire pour les professionnels</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour les professionnels : '1.2.250.1.71.4.2.1' 
+- Pour les autres : libre</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>AssociatedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>- Pour les professionnels : Valeur de l’identifiant du professionnel participant. Source : valeur de PS_IdNat (voir annexe [6]) 
+- Pour les autres : libre</t>
   </si>
   <si>
     <t>AssociatedEntity.sdtcIdentifiedBy</t>
@@ -411,10 +447,12 @@
 </t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDARoleCode</t>
+    <t>Profession / savoir-faire ou rôle : 
+- Facultatif pour les PS, non PS et systèmes 
+- Facultatif pour patient/usager</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
     <t>AssociatedEntity.addr</t>
@@ -424,6 +462,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale du participant</t>
+  </si>
+  <si>
     <t>AssociatedEntity.telecom</t>
   </si>
   <si>
@@ -431,6 +472,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom du participant</t>
+  </si>
+  <si>
     <t>AssociatedEntity.associatedPerson</t>
   </si>
   <si>
@@ -438,11 +482,17 @@
 </t>
   </si>
   <si>
+    <t>Identité du participant</t>
+  </si>
+  <si>
     <t>AssociatedEntity.scopingOrganization</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure</t>
   </si>
 </sst>
 </file>
@@ -744,7 +794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.8984375" customWidth="true" bestFit="true"/>
@@ -772,7 +822,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.6640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1298,7 +1348,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1306,10 +1356,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1407,17 +1457,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1435,11 +1485,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1490,7 +1540,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1510,17 +1560,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1538,11 +1588,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1593,7 +1643,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1613,17 +1663,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1641,11 +1691,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1654,7 +1704,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1696,7 +1746,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1716,17 +1766,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1744,11 +1794,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1799,7 +1849,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1819,10 +1869,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1849,7 +1899,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1900,7 +1950,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1920,10 +1970,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1948,7 +1998,9 @@
       <c r="K12" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1979,25 +2031,25 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2017,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2045,7 +2097,9 @@
       <c r="K13" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2096,7 +2150,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2116,21 +2170,23 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2142,10 +2198,12 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="M14" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2171,13 +2229,11 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2195,13 +2251,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
@@ -2215,16 +2271,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2241,10 +2299,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2270,11 +2330,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2292,7 +2354,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2312,21 +2374,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2338,10 +2402,12 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2391,13 +2457,13 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>74</v>
@@ -2411,21 +2477,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2437,10 +2505,14 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2490,13 +2562,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2510,16 +2582,18 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
@@ -2536,10 +2610,14 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2589,7 +2667,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2609,10 +2687,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2623,7 +2701,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2635,7 +2713,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2688,13 +2766,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2703,6 +2781,509 @@
         <v>74</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AssociatedEntity représente les caractéristiques du professionnel et/ou de l'établissement participant.</t>
+    <t>L'élément de l'en-tête du CDA associatedEntity permet de représenter les caractéristiques du professionnel et/ou de l'établissement participant.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
